--- a/Files/Madden25/IE/Season10/ExpectedContractLength.xlsx
+++ b/Files/Madden25/IE/Season10/ExpectedContractLength.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/40f61192ff96ff75/Documents/Git/MaddenTools/Files/Madden25/IE/Season9/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/40f61192ff96ff75/Documents/Git/MaddenTools/Files/Madden26/IE/Season2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6021" documentId="13_ncr:1_{ADED6FFD-BF9D-425E-B0E9-69FF67D7C25E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DA195FB-21C0-453B-97D0-CDB7E1B5304B}"/>
+  <xr:revisionPtr revIDLastSave="6052" documentId="13_ncr:1_{ADED6FFD-BF9D-425E-B0E9-69FF67D7C25E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C74B2D6-F353-4B33-97CF-8C61E3E593AE}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="24" r:id="rId1"/>
@@ -596,7 +596,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="1">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C8">
         <v>89</v>
@@ -613,7 +613,7 @@
         <v>74</v>
       </c>
       <c r="C9">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -764,7 +764,7 @@
         <v>3</v>
       </c>
       <c r="B20" s="1">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C20">
         <v>84</v>
@@ -778,10 +778,10 @@
         <v>3</v>
       </c>
       <c r="B21" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C21">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -795,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="C22">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -820,7 +820,7 @@
         <v>4</v>
       </c>
       <c r="B24" s="1">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C24">
         <v>89</v>
@@ -837,7 +837,7 @@
         <v>74</v>
       </c>
       <c r="C25">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D25">
         <v>3</v>
@@ -890,7 +890,7 @@
         <v>5</v>
       </c>
       <c r="B29" s="1">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C29">
         <v>93</v>
@@ -907,7 +907,7 @@
         <v>74</v>
       </c>
       <c r="C30">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D30">
         <v>3</v>
@@ -960,7 +960,7 @@
         <v>6</v>
       </c>
       <c r="B34" s="1">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C34">
         <v>94</v>
@@ -974,10 +974,10 @@
         <v>6</v>
       </c>
       <c r="B35" s="1">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C35">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D35">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>70</v>
       </c>
       <c r="C36">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -1030,7 +1030,7 @@
         <v>7</v>
       </c>
       <c r="B39" s="1">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C39">
         <v>93</v>
@@ -1047,7 +1047,7 @@
         <v>74</v>
       </c>
       <c r="C40">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D40">
         <v>3</v>
@@ -1100,7 +1100,7 @@
         <v>8</v>
       </c>
       <c r="B44" s="1">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C44">
         <v>89</v>
@@ -1117,7 +1117,7 @@
         <v>74</v>
       </c>
       <c r="C45">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D45">
         <v>3</v>
@@ -1394,7 +1394,7 @@
         <v>12</v>
       </c>
       <c r="B65" s="1">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C65">
         <v>79</v>
@@ -1411,7 +1411,7 @@
         <v>1</v>
       </c>
       <c r="C66">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -1520,7 +1520,7 @@
         <v>14</v>
       </c>
       <c r="B74" s="1">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C74">
         <v>79</v>
@@ -1537,7 +1537,7 @@
         <v>1</v>
       </c>
       <c r="C75">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -1576,7 +1576,7 @@
         <v>15</v>
       </c>
       <c r="B78" s="1">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C78">
         <v>84</v>
@@ -1593,7 +1593,7 @@
         <v>74</v>
       </c>
       <c r="C79">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -1758,7 +1758,7 @@
         <v>18</v>
       </c>
       <c r="B91" s="1">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C91">
         <v>77</v>
@@ -1775,7 +1775,7 @@
         <v>72</v>
       </c>
       <c r="C92">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D92">
         <v>2</v>
